--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -906,16 +906,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-1.3</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -923,16 +941,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>3.042</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1078,16 +1114,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>181.502</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -726,24 +726,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>Q1-26 y/y</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF / Statistics Agency</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun-26</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2025 actual 7.7%; Q1-26 8.7% y/y</t>
-        </is>
-      </c>
+          <t>01-Jun-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jul-26</t>
+          <t>01-Jul-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -835,19 +831,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Economy and Finance</t>
+          <t>Ministry of Economy and Finance / IMF Article IV (consolidated budget)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jun-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
+          <t>01-Jun-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1001,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves incl. gold (~90%)</t>
+          <t>gross international reserves incl. gold (~90% gold, ~439 tonnes)</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1299,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>None active (annual Article IV surveillance and technical assistance only)</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1351,10 +1343,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>2027F</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1370,7 +1367,8 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1386,11 +1384,14 @@
         <v>6.8</v>
       </c>
       <c r="E3" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>IMF / Statistics Agency, Jun-26</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>IMF / Statistics Agency, Jun-26 (2025 actual; 2026F and 2027F IMF projections)</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1405,8 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1416,7 +1418,8 @@
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1430,11 +1433,14 @@
       <c r="C6" s="2" t="n">
         <v>-2.1</v>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>IMF / Ministry of Economy and Finance, Jun-26</t>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ministry of Economy and Finance / IMF Article IV, Jun-26 (2024, 2025 actuals; 2026E is the government target of ~2.5%)</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1454,8 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1457,12 +1464,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="n">
+        <v>31.9</v>
+      </c>
       <c r="D8" s="2" t="n">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="n"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ministry of Economy and Finance, 01-Jul-26 (end-2025 level)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1474,7 +1488,8 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1486,7 +1501,8 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1498,7 +1514,8 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1510,7 +1527,8 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uzbekistan.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uzbekistan.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt $48.31bn ($40.71bn external, $7.60bn domestic)</t>
+          <t>total public debt (external $40.71bn + domestic $7.60bn = $48.31bn)</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance / IMF Article IV (consolidated budget)</t>
+          <t>Ministry of Economy and Finance (consolidated budget)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01-Jun-26</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves incl. gold (~90% gold, ~439 tonnes)</t>
+          <t>gross international reserves incl. gold (~90% of total)</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IMF / Statistics Agency, Jun-26 (2025 actual; 2026F and 2027F IMF projections)</t>
+          <t>IMF / Statistics Agency, 01-Jun-26 (2026E and 2027F are IMF projections)</t>
         </is>
       </c>
     </row>
@@ -1436,11 +1436,13 @@
       <c r="D6" s="2" t="n">
         <v>-2.5</v>
       </c>
-      <c r="E6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance / IMF Article IV, Jun-26 (2024, 2025 actuals; 2026E is the government target of ~2.5%)</t>
+          <t>Ministry of Economy and Finance / IMF Article IV, 2024-25 actuals; 2026F is the government target, 01-Jul-26</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1476,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 01-Jul-26 (end-2025 level)</t>
+          <t>Ministry of Economy and Finance, 01-Jul-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF / Statistics Agency</t>
+          <t>Statistics Agency (per IMF / Statistics Agency)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves incl. gold (~90% of total)</t>
+          <t>gross official international reserves incl. gold (~90% gold)</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None active (annual Article IV surveillance and technical assistance only)</t>
+          <t>None (annual Article IV surveillance only)</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IMF / Statistics Agency, 01-Jun-26 (2026E and 2027F are IMF projections)</t>
+          <t>IMF / Statistics Agency, Jun-26 (2025 actual; 2026E and 2027F IMF projections)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance / IMF Article IV, 2024-25 actuals; 2026F is the government target, 01-Jul-26</t>
+          <t>IMF / Ministry of Economy and Finance, Jun-26 (2026E is the government target of ~2.5% of GDP)</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 01-Jul-26</t>
+          <t>Ministry of Economy and Finance, 01-Jul-26 (end-2025 level)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Statistics Agency (per IMF / Statistics Agency)</t>
+          <t>IMF / Statistics Agency</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance (consolidated budget)</t>
+          <t>Ministry of Economy and Finance / IMF Article IV (consolidated budget)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross official international reserves incl. gold (~90% gold)</t>
+          <t>gross international reserves incl. gold (~90% gold, ~439 tonnes)</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (annual Article IV surveillance only)</t>
+          <t>None (Article IV surveillance only)</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IMF / Statistics Agency, Jun-26 (2025 actual; 2026E and 2027F IMF projections)</t>
+          <t>IMF / Statistics Agency, Jun-26 (2025 actual; 2026F and 2027F IMF projections)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Economy and Finance, Jun-26 (2026E is the government target of ~2.5% of GDP)</t>
+          <t>Ministry of Economy and Finance / IMF Article IV, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 01-Jul-26 (end-2025 level)</t>
+          <t>Ministry of Economy and Finance, 01-Jul-26 (end-2025 value)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF / Statistics Agency</t>
+          <t>Statistics Agency / IMF</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt (external $40.71bn + domestic $7.60bn = $48.31bn)</t>
+          <t>total public debt ($48.31bn: $40.71bn external, $7.60bn domestic)</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance / IMF Article IV (consolidated budget)</t>
+          <t>Ministry of Economy and Finance / IMF Article IV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>01-Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (Article IV surveillance only)</t>
+          <t>None active (Article IV surveillance and technical assistance only)</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IMF / Statistics Agency, Jun-26 (2025 actual; 2026F and 2027F IMF projections)</t>
+          <t>2025 actual: IMF / Statistics Agency, 01-Jun-26; 2026E and 2027F: IMF projections, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance / IMF Article IV, Jun-26</t>
+          <t>2024 and 2025: IMF Article IV / Ministry of Economy and Finance, 01-Jun-26; 2026F is the government target, Ministry of Economy and Finance, 01-Jul-26</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 01-Jul-26 (end-2025 value)</t>
+          <t>Ministry of Economy and Finance, 01-Jul-26 (end-2025 level)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -831,12 +831,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance / IMF Article IV</t>
+          <t>IMF Article IV / Ministry of Economy and Finance (consolidated)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025 actual: IMF / Statistics Agency, 01-Jun-26; 2026E and 2027F: IMF projections, Jun-26</t>
+          <t>IMF / Statistics Agency, Jun-26 (2026E and 2027F are IMF projections)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2024 and 2025: IMF Article IV / Ministry of Economy and Finance, 01-Jun-26; 2026F is the government target, Ministry of Economy and Finance, 01-Jul-26</t>
+          <t>IMF Article IV / Ministry of Economy and Finance, Jun-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uzbekistan.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uzbekistan.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uzbekistan.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uzbekistan.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Uzbekistan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uzbekistan.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uzbekistan.json</t>
         </is>
       </c>
     </row>
